--- a/Paper/_output/_comparison/crisis_analysis_variable_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_monthly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -453,18 +453,22 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,62 +539,82 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_full</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_full</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ptt</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ptt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ttp</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ttp</t>
         </is>
       </c>
     </row>
@@ -640,34 +664,34 @@
       <c r="M2" t="b">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>2250</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="3" t="n">
-        <v>-0.5233370252427425</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="3" t="n">
         <v>-0.5233370252427425</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="R2" s="3" t="n">
+        <v>-0.5233370252427425</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>888</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" s="3" t="n">
         <v>1.097918346834583</v>
       </c>
-      <c r="W2" s="3" t="inlineStr"/>
       <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -715,39 +739,51 @@
       <c r="M3" t="b">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>355</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" s="3" t="n">
-        <v>-0.5562460462241584</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" s="3" t="n">
         <v>-0.5562460462241584</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R3" s="3" t="n">
+        <v>-0.5562460462241584</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>994</v>
       </c>
-      <c r="T3" t="n">
-        <v>106</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" s="3" t="n">
         <v>1.253501048252387</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>0.5</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -796,39 +832,51 @@
       <c r="M4" t="b">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>579</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" s="3" t="n">
-        <v>-0.5405877541480399</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" s="3" t="n">
         <v>-0.5405877541480399</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R4" s="3" t="n">
+        <v>-0.5405877541480399</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>2427</v>
       </c>
-      <c r="T4" t="n">
-        <v>1539</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" s="3" t="n">
         <v>1.176694263222226</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>0.4</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y4" s="3" t="n">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="n">
         <v>0.4</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -877,39 +925,51 @@
       <c r="M5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>355</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" s="3" t="n">
-        <v>-0.4557974809248458</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>-0.4557974809248458</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R5" s="3" t="n">
+        <v>-0.4557974809248458</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>712</v>
       </c>
-      <c r="T5" t="n">
-        <v>-176</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" s="3" t="n">
         <v>0.837551214756322</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>0.6666666666666666</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -958,39 +1018,51 @@
       <c r="M6" t="b">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>353</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" s="3" t="n">
-        <v>-0.615775334514046</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
         <v>-0.615775334514046</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R6" s="3" t="n">
+        <v>-0.615775334514046</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>1045</v>
       </c>
-      <c r="T6" t="n">
-        <v>157</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" s="3" t="n">
         <v>1.602643947220918</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="X6" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X6" s="3" t="n">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y6" s="3" t="n">
-        <v>0.5</v>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1039,39 +1111,51 @@
       <c r="M7" t="b">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>353</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" s="3" t="n">
-        <v>-0.6100001664268991</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
         <v>-0.6100001664268991</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R7" s="3" t="n">
+        <v>-0.6100001664268991</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>1102</v>
       </c>
-      <c r="T7" t="n">
-        <v>214</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" s="3" t="n">
         <v>1.564103658296977</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="X7" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y7" s="3" t="n">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1120,39 +1204,51 @@
       <c r="M8" t="b">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>353</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" s="3" t="n">
-        <v>-0.6146619938319895</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
         <v>-0.6146619938319895</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R8" s="3" t="n">
+        <v>-0.6146619938319895</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>1102</v>
       </c>
-      <c r="T8" t="n">
-        <v>214</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" s="3" t="n">
         <v>1.595124238962278</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="X8" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>0.5</v>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1166,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1180,17 +1276,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1251,55 +1350,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -1343,35 +1457,44 @@
       <c r="K2" s="3" t="n">
         <v>0.2657575172078731</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
+      <c r="L2" s="3" t="n">
+        <v>0.2657575172078731</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" s="3" t="n">
+        <v>-0.03939252582909292</v>
+      </c>
+      <c r="Q2" t="n">
         <v>583</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>-55</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>-0.4859401977791236</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.486230944244141</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>1313</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="b">
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="Y2" s="3" t="n">
         <v>0.9452989626493482</v>
       </c>
     </row>
@@ -1415,35 +1538,42 @@
       <c r="K3" s="3" t="n">
         <v>0.1651097235934952</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1531905859315117</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>583</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>-55</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>-0.3722353067637153</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.3927946397031032</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>1049</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="b">
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="Y3" s="3" t="n">
         <v>0.5929535553277914</v>
       </c>
     </row>
@@ -1485,35 +1615,44 @@
       <c r="K4" s="3" t="n">
         <v>0.3318786120147709</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
+      <c r="L4" s="3" t="n">
+        <v>0.3318786120147709</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" s="3" t="n">
+        <v>-0.07379561685859526</v>
+      </c>
+      <c r="Q4" t="n">
         <v>583</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>-55</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-0.5351953756562349</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.5405877541480402</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>1313</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="b">
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="Y4" s="3" t="n">
         <v>1.151441589919315</v>
       </c>
     </row>
@@ -1557,35 +1696,42 @@
       <c r="K5" s="3" t="n">
         <v>0.1481278166620073</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1055945425444167</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>583</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>-55</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="S5" s="3" t="n">
         <v>-0.3030216391542161</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.3432461105733071</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>380</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="b">
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="Y5" s="3" t="n">
         <v>0.4347647734522189</v>
       </c>
     </row>
@@ -1629,35 +1775,42 @@
       <c r="K6" s="3" t="n">
         <v>0.1480346777153202</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.1366736544747824</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>638</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.3687277122325638</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.3857020660410981</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>978</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="b">
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="Y6" s="3" t="n">
         <v>0.5841024853737995</v>
       </c>
     </row>
@@ -1701,35 +1854,42 @@
       <c r="K7" s="3" t="n">
         <v>0.1513752318139535</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.1393683562842672</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>638</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.3754608976947175</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.3957852429007654</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>969</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="b">
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="Y7" s="3" t="n">
         <v>0.601180768840295</v>
       </c>
     </row>
@@ -1773,35 +1933,42 @@
       <c r="K8" s="3" t="n">
         <v>0.1716566383260633</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.1505409261939787</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>638</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.3976227638230778</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.4221174890977989</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>820</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="b">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="Y8" s="3" t="n">
         <v>0.6600892927937492</v>
       </c>
     </row>
@@ -1816,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1830,17 +1997,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1901,55 +2071,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -1995,37 +2180,44 @@
       <c r="K2" s="3" t="n">
         <v>0.2352416489517779</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.2149811169453122</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>355</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.503509252857314</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.5040024023286778</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>860</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>1.014136226616547</v>
       </c>
     </row>
@@ -2069,37 +2261,44 @@
       <c r="K3" s="3" t="n">
         <v>0.2498952241815955</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.2406268872379813</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>355</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.556246046224159</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.556246046224159</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>994</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>134</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>1.253501048252389</v>
       </c>
     </row>
@@ -2143,37 +2342,44 @@
       <c r="K4" s="3" t="n">
         <v>0.2093201856322416</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.1581360678574537</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>355</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.4375057689528339</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.4456113326384448</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>475</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>-385</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.7777960107045938</v>
       </c>
     </row>
@@ -2217,37 +2423,44 @@
       <c r="K5" s="3" t="n">
         <v>0.1974000942251041</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1690644494153121</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>355</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.4557974809248457</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.4557974809248457</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>712</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-148</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.8375512147563215</v>
       </c>
     </row>
@@ -2291,37 +2504,44 @@
       <c r="K6" s="3" t="n">
         <v>0.2811987286404189</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.2756395438708416</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>353</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>-2</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="S6" s="3" t="n">
         <v>-0.6157753345140465</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.6157753345140465</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>1045</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>185</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>1.602643947220921</v>
       </c>
     </row>
@@ -2365,37 +2585,44 @@
       <c r="K7" s="3" t="n">
         <v>0.2848395462178516</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.2848395462178516</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>353</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>-2</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="S7" s="3" t="n">
         <v>-0.6100001664268992</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.6100001664268992</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>1102</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>242</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>1.564103658296978</v>
       </c>
     </row>
@@ -2439,37 +2666,44 @@
       <c r="K8" s="3" t="n">
         <v>0.2982796480008626</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.2982796480008626</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>353</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>-2</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="S8" s="3" t="n">
         <v>-0.6146619938319893</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.6146619938319893</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>1102</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>242</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>1.595124238962276</v>
       </c>
     </row>
@@ -2484,7 +2718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2498,17 +2732,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2569,55 +2806,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -2663,37 +2915,44 @@
       <c r="K2" s="3" t="n">
         <v>0.08269444253856417</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.07912714930396605</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>64</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.1954368693665688</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.2022979914860074</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>76</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.2429105460160741</v>
       </c>
     </row>
@@ -2737,37 +2996,44 @@
       <c r="K3" s="3" t="n">
         <v>0.05923389423926628</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.05315214159940083</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>64</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.1661942153206122</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.1661942153206122</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>59</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>-17</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.1993200555504859</v>
       </c>
     </row>
@@ -2811,37 +3077,44 @@
       <c r="K4" s="3" t="n">
         <v>0.07930286943495034</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.07930286943495034</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>64</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.1972404039901224</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.1989196555792887</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>89</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>13</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.2457029538737467</v>
       </c>
     </row>
@@ -2885,37 +3158,44 @@
       <c r="K5" s="3" t="n">
         <v>0.04899572133157781</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.04396515797967676</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>64</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.1425767900867722</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.1452798889626855</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>59</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-17</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.1662852001652733</v>
       </c>
     </row>
@@ -2959,37 +3239,44 @@
       <c r="K6" s="3" t="n">
         <v>0.06265132539194433</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.05800385632525248</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>64</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.1804269089298145</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.1804269089298145</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>67</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-9</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.2201474290648269</v>
       </c>
     </row>
@@ -3033,37 +3320,44 @@
       <c r="K7" s="3" t="n">
         <v>0.06178239628542021</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.05408108450021022</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>64</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.1756429698727684</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.1758389292270287</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>53</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-23</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.2130666245979118</v>
       </c>
     </row>
@@ -3107,37 +3401,44 @@
       <c r="K8" s="3" t="n">
         <v>0.05450903553707552</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.04627747201120846</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>64</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.161539993759288</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.161539993759288</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>46</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-30</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.1926627299536476</v>
       </c>
     </row>
@@ -3152,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3166,17 +3467,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3237,55 +3541,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -3331,37 +3650,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1403286526425155</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.1061745325998058</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>23</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.2902196151348785</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.2902196151348785</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>55</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.4088864968986547</v>
       </c>
     </row>
@@ -3405,37 +3731,44 @@
       <c r="K3" s="3" t="n">
         <v>0.1285134533062128</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1203377080590004</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>23</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.3081513905894094</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.3081513905894094</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>97</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>42</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.4454029196530931</v>
       </c>
     </row>
@@ -3479,37 +3812,44 @@
       <c r="K4" s="3" t="n">
         <v>0.1291668938515992</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.11842425666514</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>23</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.3158142431874948</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.3158142431874948</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>92</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>37</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.4615913734580137</v>
       </c>
     </row>
@@ -3553,37 +3893,44 @@
       <c r="K5" s="3" t="n">
         <v>0.1183626651723915</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1135473630461201</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>23</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.295950620638614</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.295950620638614</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>103</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>48</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.4203549201436105</v>
       </c>
     </row>
@@ -3627,37 +3974,44 @@
       <c r="K6" s="3" t="n">
         <v>0.1330355594692814</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.1255974299978942</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>23</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.3225249683879728</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.3225249683879728</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>99</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>44</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.4760691587711159</v>
       </c>
     </row>
@@ -3701,37 +4055,44 @@
       <c r="K7" s="3" t="n">
         <v>0.1443875768739651</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.1443875768739651</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>23</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.341225014720676</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.341225014720676</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>114</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>59</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.5179689914546388</v>
       </c>
     </row>
@@ -3775,37 +4136,44 @@
       <c r="K8" s="3" t="n">
         <v>0.1293734448870105</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.1270081001689617</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>23</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.3207580395918463</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.3207580395918463</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>109</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>54</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.4722294238110734</v>
       </c>
     </row>
@@ -3820,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3834,17 +4202,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3905,55 +4276,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -3999,37 +4385,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1873955345996986</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>253</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>58</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>-0.3239608533428741</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.3239608533428741</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>220</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.4792042812088524</v>
       </c>
     </row>
@@ -4073,37 +4466,44 @@
       <c r="K3" s="3" t="n">
         <v>0.1702877757340237</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1536695977132047</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>195</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.291261694520513</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.291261694520513</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>190</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>-30</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.410958025365179</v>
       </c>
     </row>
@@ -4147,37 +4547,44 @@
       <c r="K4" s="3" t="n">
         <v>0.1845225032964088</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.1665151754338592</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>253</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>58</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-0.2867967086275238</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.2867967086275238</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>132</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>-88</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.4021247687677061</v>
       </c>
     </row>
@@ -4221,37 +4628,44 @@
       <c r="K5" s="3" t="n">
         <v>0.1318162553441144</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1201788129608711</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>195</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.2377598766809245</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.2377598766809245</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>198</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-22</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.3119225417387239</v>
       </c>
     </row>
@@ -4295,37 +4709,44 @@
       <c r="K6" s="3" t="n">
         <v>0.2035103799588042</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.1785845264540923</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>197</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="S6" s="3" t="n">
         <v>-0.3287615049188402</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.3287615049188402</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>167</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-53</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.4897834485477317</v>
       </c>
     </row>
@@ -4369,37 +4790,44 @@
       <c r="K7" s="3" t="n">
         <v>0.2115738387606444</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.1856603766981939</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>197</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="S7" s="3" t="n">
         <v>-0.3381261530483139</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.3381261530483139</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>167</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-53</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.5108619332907343</v>
       </c>
     </row>
@@ -4443,37 +4871,44 @@
       <c r="K8" s="3" t="n">
         <v>0.206522304676247</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.180481244645591</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>211</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>16</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="S8" s="3" t="n">
         <v>-0.3380397400935387</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.3380397400935387</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>150</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-70</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.5106647038619894</v>
       </c>
     </row>
@@ -4488,7 +4923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4502,17 +4937,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4573,55 +5011,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -4667,37 +5120,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1032426212645823</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.08367967670060686</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>34</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.2242012270138081</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.2242012270138081</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>55</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.2889940469367029</v>
       </c>
     </row>
@@ -4741,37 +5201,44 @@
       <c r="K3" s="3" t="n">
         <v>0.08442450091433044</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.06993138750699741</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>34</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.1872487154673582</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.1872487154673582</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>59</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.2303887044300794</v>
       </c>
     </row>
@@ -4815,37 +5282,44 @@
       <c r="K4" s="3" t="n">
         <v>0.08882055381815625</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.07701437681681529</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>32</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>-2</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-0.1919673527633516</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.1919673527633516</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>70</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>15</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.2375737582136705</v>
       </c>
     </row>
@@ -4889,37 +5363,44 @@
       <c r="K5" s="3" t="n">
         <v>0.06216000016109517</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.06216000016109517</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>34</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.1513632279065376</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.1513632279065376</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>102</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>47</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.1783604398064753</v>
       </c>
     </row>
@@ -4963,37 +5444,44 @@
       <c r="K6" s="3" t="n">
         <v>0.09126633999965644</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.07519549547653598</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>34</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.1891226670882522</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.1891226670882522</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>58</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.2332321541276028</v>
       </c>
     </row>
@@ -5037,37 +5525,44 @@
       <c r="K7" s="3" t="n">
         <v>0.09334112666390186</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.07438277583171804</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>34</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.1965679708822623</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.1965679708822623</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>52</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-3</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.2446603617459924</v>
       </c>
     </row>
@@ -5111,37 +5606,44 @@
       <c r="K8" s="3" t="n">
         <v>0.08170799359290759</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.06659244470335765</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>34</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.1711634614757399</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.1711634614757399</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>56</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.2065105162719971</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_monthly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -882,12 +882,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -896,28 +896,28 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>39364</v>
+        <v>39442</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40911</v>
+        <v>40533</v>
       </c>
       <c r="G5" t="n">
-        <v>1067</v>
+        <v>753</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.3744774130256877</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.3744774130256877</v>
       </c>
       <c r="J5" t="n">
-        <v>1066</v>
+        <v>752</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1974000942251045</v>
+        <v>0.1599384989554068</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -927,25 +927,25 @@
       </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>355</v>
+        <v>301</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.3744774130256877</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.3744774130256877</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>712</v>
+        <v>452</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>0.837551214756322</v>
+        <v>0.5986632950171407</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -992,25 +992,25 @@
         <v>39364</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>39877</v>
+        <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>41394</v>
+        <v>40911</v>
       </c>
       <c r="G6" t="n">
-        <v>1398</v>
+        <v>1067</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="J6" t="n">
-        <v>1397</v>
+        <v>1066</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2811987286404182</v>
+        <v>0.1974000942251045</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1020,60 +1020,60 @@
       </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1045</v>
+        <v>712</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>1.602643947220918</v>
+        <v>0.837551214756322</v>
       </c>
       <c r="X6" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1088,22 +1088,22 @@
         <v>39877</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41477</v>
+        <v>41394</v>
       </c>
       <c r="G7" t="n">
-        <v>1455</v>
+        <v>1398</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="J7" t="n">
-        <v>1454</v>
+        <v>1397</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2848395462178512</v>
+        <v>0.2811987286404182</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1117,21 +1117,21 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1102</v>
+        <v>1045</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>1.564103658296977</v>
+        <v>1.602643947220918</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>0.6666666666666666</v>
@@ -1150,23 +1150,23 @@
         </is>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1187,16 +1187,16 @@
         <v>1455</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.6146619938319895</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.6146619938319895</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="J8" t="n">
         <v>1454</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.298279648000863</v>
+        <v>0.2848395462178512</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -1210,10 +1210,10 @@
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
-        <v>-0.6146619938319895</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-0.6146619938319895</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1224,7 +1224,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>1.595124238962278</v>
+        <v>1.564103658296977</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0.6666666666666666</v>
@@ -1243,9 +1243,102 @@
         </is>
       </c>
       <c r="AB8" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>39877</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1455</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.6146619938319895</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.6146619938319895</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1454</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.298279648000863</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>353</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>-0.6146619938319895</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>-0.6146619938319895</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1102</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" s="3" t="n">
+        <v>1.595124238962278</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1262,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1659,12 +1752,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1679,25 +1772,25 @@
         <v>37460</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38012</v>
+        <v>37783</v>
       </c>
       <c r="G5" t="n">
-        <v>963</v>
+        <v>806</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.2185683866529438</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.3180206894883698</v>
       </c>
       <c r="J5" t="n">
-        <v>829</v>
+        <v>292</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1481278166620073</v>
+        <v>0.1252308092487745</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1055945425444167</v>
+        <v>0.08167972914679614</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>39364</v>
@@ -1716,34 +1809,34 @@
         <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.2185683866529438</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.3180206894883698</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>380</v>
+        <v>223</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4347647734522189</v>
+        <v>0.2797025138473266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1755,28 +1848,28 @@
         <v>36608</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37538</v>
+        <v>37460</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38957</v>
+        <v>38012</v>
       </c>
       <c r="G6" t="n">
-        <v>1616</v>
+        <v>963</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3687277122325638</v>
+        <v>-0.3030216391542161</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.3432461105733071</v>
       </c>
       <c r="J6" t="n">
-        <v>1586</v>
+        <v>829</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1480346777153202</v>
+        <v>0.1481278166620073</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1366736544747824</v>
+        <v>0.1055945425444167</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>39364</v>
@@ -1789,40 +1882,40 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>638</v>
+        <v>583</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3687277122325638</v>
+        <v>-0.3030216391542161</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.3432461105733071</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>978</v>
+        <v>380</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
         <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.5841024853737995</v>
+        <v>0.4347647734522189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1837,25 +1930,25 @@
         <v>37538</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38944</v>
+        <v>38957</v>
       </c>
       <c r="G7" t="n">
-        <v>1607</v>
+        <v>1616</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3754608976947175</v>
+        <v>-0.3687277122325638</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.3857020660410981</v>
       </c>
       <c r="J7" t="n">
-        <v>1572</v>
+        <v>1586</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1513752318139535</v>
+        <v>0.1480346777153202</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1393683562842672</v>
+        <v>0.1366736544747824</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>39364</v>
@@ -1874,34 +1967,34 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3754608976947175</v>
+        <v>-0.3687277122325638</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.3857020660410981</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.601180768840295</v>
+        <v>0.5841024853737995</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1916,25 +2009,25 @@
         <v>37538</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38728</v>
+        <v>38944</v>
       </c>
       <c r="G8" t="n">
-        <v>1458</v>
+        <v>1607</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3976227638230778</v>
+        <v>-0.3754608976947175</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4221174890977989</v>
+        <v>-0.3957852429007654</v>
       </c>
       <c r="J8" t="n">
-        <v>1386</v>
+        <v>1572</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1716566383260633</v>
+        <v>0.1513752318139535</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1505409261939787</v>
+        <v>0.1393683562842672</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>39364</v>
@@ -1953,22 +2046,101 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3976227638230778</v>
+        <v>-0.3754608976947175</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.4221174890977989</v>
+        <v>-0.3957852429007654</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>820</v>
+        <v>969</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>0.601180768840295</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>36608</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>38728</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1458</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.3976227638230778</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.4221174890977989</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1386</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.1716566383260633</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.1505409261939787</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>638</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.3976227638230778</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.4221174890977989</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>820</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.6600892927937492</v>
       </c>
     </row>
@@ -1983,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2181,10 +2353,10 @@
         <v>0.2352416489517779</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2149811169453122</v>
+        <v>0.1561727120528913</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>41477</v>
+        <v>43364</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2262,10 +2434,10 @@
         <v>0.2498952241815955</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2406268872379813</v>
+        <v>0.1748030436662044</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>41477</v>
+        <v>43364</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -2343,10 +2515,10 @@
         <v>0.2093201856322416</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1581360678574537</v>
+        <v>0.1148777108501162</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>41477</v>
+        <v>43364</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -2386,12 +2558,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2406,28 +2578,28 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40911</v>
+        <v>40533</v>
       </c>
       <c r="G5" t="n">
-        <v>1067</v>
+        <v>807</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="J5" t="n">
-        <v>1066</v>
+        <v>805</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1974000942251041</v>
+        <v>0.1546755474705558</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1690644494153121</v>
+        <v>0.08370501759350023</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>41477</v>
+        <v>43364</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -2443,36 +2615,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>712</v>
+        <v>452</v>
       </c>
       <c r="W5" t="n">
-        <v>-148</v>
+        <v>-408</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.8375512147563215</v>
+        <v>0.5983357204467421</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2484,31 +2656,31 @@
         <v>39364</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>39877</v>
+        <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>41394</v>
+        <v>40911</v>
       </c>
       <c r="G6" t="n">
-        <v>1398</v>
+        <v>1067</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="J6" t="n">
-        <v>1397</v>
+        <v>1066</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2811987286404189</v>
+        <v>0.1974000942251041</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2756395438708416</v>
+        <v>0.1228166173480004</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>41477</v>
+        <v>43364</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -2518,42 +2690,42 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="R6" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1045</v>
+        <v>712</v>
       </c>
       <c r="W6" t="n">
-        <v>185</v>
+        <v>-148</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1.602643947220921</v>
+        <v>0.8375512147563215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2568,28 +2740,28 @@
         <v>39877</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41477</v>
+        <v>41394</v>
       </c>
       <c r="G7" t="n">
-        <v>1455</v>
+        <v>1398</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="J7" t="n">
-        <v>1454</v>
+        <v>1397</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2848395462178516</v>
+        <v>0.2811987286404189</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2848395462178516</v>
+        <v>0.2002379359033743</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>41477</v>
+        <v>43364</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -2605,36 +2777,36 @@
         <v>-2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1102</v>
+        <v>1045</v>
       </c>
       <c r="W7" t="n">
-        <v>242</v>
+        <v>185</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.564103658296978</v>
+        <v>1.602643947220921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2655,22 +2827,22 @@
         <v>1455</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="J8" t="n">
         <v>1454</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2982796480008626</v>
+        <v>0.2848395462178516</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.2982796480008626</v>
+        <v>0.2069212638990652</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>41477</v>
+        <v>43364</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -2686,10 +2858,10 @@
         <v>-2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -2704,6 +2876,87 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>1.564103658296978</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>39877</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>41477</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1455</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.6146619938319893</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.6146619938319893</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1454</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.2982796480008626</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.2166848058116959</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>43364</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>353</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.6146619938319893</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.6146619938319893</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1102</v>
+      </c>
+      <c r="W9" t="n">
+        <v>242</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>1.595124238962276</v>
       </c>
     </row>
@@ -2718,7 +2971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2916,10 +3169,10 @@
         <v>0.08269444253856417</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.07912714930396605</v>
+        <v>0.0521896337568788</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>43588</v>
+        <v>43880</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2997,10 +3250,10 @@
         <v>0.05923389423926628</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.05315214159940083</v>
+        <v>0.0350573833111343</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>43588</v>
+        <v>43880</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3078,10 +3331,10 @@
         <v>0.07930286943495034</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.07930286943495034</v>
+        <v>0.05230553290603873</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>43588</v>
+        <v>43880</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3121,12 +3374,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3141,28 +3394,28 @@
         <v>43458</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43545</v>
+        <v>43563</v>
       </c>
       <c r="G5" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.1360620360985055</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.143729669862375</v>
       </c>
       <c r="J5" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.04849898132196487</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.04396515797967676</v>
+        <v>0.03006079347508416</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>43588</v>
+        <v>43880</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3178,36 +3431,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.1360620360985055</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.143729669862375</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="W5" t="n">
-        <v>-17</v>
+        <v>-5</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.1574905164302043</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3222,28 +3475,28 @@
         <v>43458</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43557</v>
+        <v>43545</v>
       </c>
       <c r="G6" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="J6" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.06265132539194433</v>
+        <v>0.04899572133157781</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.05800385632525248</v>
+        <v>0.02899795472484739</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>43588</v>
+        <v>43880</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3259,36 +3512,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="W6" t="n">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.2201474290648269</v>
+        <v>0.1662852001652733</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3303,28 +3556,28 @@
         <v>43458</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43537</v>
+        <v>43557</v>
       </c>
       <c r="G7" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="J7" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06178239628542021</v>
+        <v>0.06265132539194433</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.05408108450021022</v>
+        <v>0.03825741284413761</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43588</v>
+        <v>43880</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -3340,36 +3593,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="W7" t="n">
-        <v>-23</v>
+        <v>-9</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2130666245979118</v>
+        <v>0.2201474290648269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3384,28 +3637,28 @@
         <v>43458</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43528</v>
+        <v>43537</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.1756429698727684</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.1758389292270287</v>
       </c>
       <c r="J8" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.05450903553707552</v>
+        <v>0.06178239628542021</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.04627747201120846</v>
+        <v>0.03567008312656749</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>43588</v>
+        <v>43880</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -3421,24 +3674,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.1756429698727684</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.1758389292270287</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>53</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-23</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.2130666245979118</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>43364</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>43528</v>
+      </c>
+      <c r="G9" t="n">
+        <v>110</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.161539993759288</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.161539993759288</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>109</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.05450903553707552</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.03052308008950504</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>64</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.161539993759288</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.161539993759288</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>46</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>-30</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.1926627299536476</v>
       </c>
     </row>
@@ -3453,7 +3787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3651,10 +3985,10 @@
         <v>0.1403286526425155</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1061745325998058</v>
+        <v>0.05728893254440421</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>44076</v>
+        <v>44564</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -3732,10 +4066,10 @@
         <v>0.1285134533062128</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1203377080590004</v>
+        <v>0.06493100247990062</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>44076</v>
+        <v>44564</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3813,10 +4147,10 @@
         <v>0.1291668938515992</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.11842425666514</v>
+        <v>0.06389855538410746</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44076</v>
+        <v>44564</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3856,12 +4190,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3876,28 +4210,28 @@
         <v>43913</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>44061</v>
+        <v>44055</v>
       </c>
       <c r="G5" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="J5" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1183626651723915</v>
+        <v>0.1193940004707371</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1135473630461201</v>
+        <v>0.0608199262236669</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44076</v>
+        <v>44564</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3913,36 +4247,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="W5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.4071307910896131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3957,28 +4291,28 @@
         <v>43913</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>44055</v>
+        <v>44061</v>
       </c>
       <c r="G6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="J6" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1330355594692814</v>
+        <v>0.1183626651723915</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1255974299978942</v>
+        <v>0.0612671142774218</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44076</v>
+        <v>44564</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3994,36 +4328,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="W6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4760691587711159</v>
+        <v>0.4203549201436105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4038,28 +4372,28 @@
         <v>43913</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>44076</v>
+        <v>44055</v>
       </c>
       <c r="G7" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="J7" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1443875768739651</v>
+        <v>0.1330355594692814</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1443875768739651</v>
+        <v>0.06776900748902423</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44076</v>
+        <v>44564</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4075,36 +4409,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="W7" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5179689914546388</v>
+        <v>0.4760691587711159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4119,28 +4453,28 @@
         <v>43913</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>44069</v>
+        <v>44076</v>
       </c>
       <c r="G8" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="J8" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1293734448870105</v>
+        <v>0.1443875768739651</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1270081001689617</v>
+        <v>0.07790766720830088</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44076</v>
+        <v>44564</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4156,24 +4490,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>114</v>
+      </c>
+      <c r="W8" t="n">
+        <v>59</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.5179689914546388</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="G9" t="n">
+        <v>132</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.3207580395918463</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.3207580395918463</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>131</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.1293734448870105</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.06853016731044111</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>23</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.3207580395918463</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.3207580395918463</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>109</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>54</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.4722294238110734</v>
       </c>
     </row>
@@ -4188,7 +4603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4386,10 +4801,10 @@
         <v>0.1873955345996986</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1873955345996986</v>
+        <v>0.1456175032694572</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45250</v>
+        <v>45707</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -4467,10 +4882,10 @@
         <v>0.1702877757340237</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1536695977132047</v>
+        <v>0.1194104395028351</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45250</v>
+        <v>45707</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -4548,10 +4963,10 @@
         <v>0.1845225032964088</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1665151754338592</v>
+        <v>0.1293922192700595</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45250</v>
+        <v>45707</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -4591,12 +5006,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4608,31 +5023,31 @@
         <v>44564</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44846</v>
+        <v>44729</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45135</v>
+        <v>45317</v>
       </c>
       <c r="G5" t="n">
-        <v>393</v>
+        <v>518</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.2223141762956242</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.2223141762956242</v>
       </c>
       <c r="J5" t="n">
-        <v>392</v>
+        <v>517</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1318162553441144</v>
+        <v>0.1212946577391739</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1201788129608711</v>
+        <v>0.0986257965760659</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>45250</v>
+        <v>45707</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -4642,42 +5057,42 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>195</v>
+        <v>115</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.2223141762956242</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.2223141762956242</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>198</v>
+        <v>403</v>
       </c>
       <c r="W5" t="n">
-        <v>-22</v>
+        <v>183</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.3119225417387239</v>
+        <v>0.2858663094007141</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4689,31 +5104,31 @@
         <v>44564</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44848</v>
+        <v>44846</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45092</v>
+        <v>45135</v>
       </c>
       <c r="G6" t="n">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="J6" t="n">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2035103799588042</v>
+        <v>0.1318162553441144</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1785845264540923</v>
+        <v>0.09338610296468229</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45250</v>
+        <v>45707</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -4723,42 +5138,42 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="W6" t="n">
-        <v>-53</v>
+        <v>-22</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4897834485477317</v>
+        <v>0.3119225417387239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4779,22 +5194,22 @@
         <v>364</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="J7" t="n">
         <v>363</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2115738387606444</v>
+        <v>0.2035103799588042</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1856603766981939</v>
+        <v>0.138770824610914</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45250</v>
+        <v>45707</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4810,10 +5225,10 @@
         <v>2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -4828,18 +5243,18 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5108619332907343</v>
+        <v>0.4897834485477317</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4851,31 +5266,31 @@
         <v>44564</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44868</v>
+        <v>44848</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45089</v>
+        <v>45092</v>
       </c>
       <c r="G8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3380397400935387</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3380397400935387</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="J8" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.206522304676247</v>
+        <v>0.2115738387606444</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.180481244645591</v>
+        <v>0.1442691821265061</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45250</v>
+        <v>45707</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4885,30 +5300,111 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
+        <v>197</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>167</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-53</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.5108619332907343</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>44868</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>45089</v>
+      </c>
+      <c r="G9" t="n">
+        <v>361</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.3380397400935387</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.3380397400935387</v>
+      </c>
+      <c r="J9" t="n">
+        <v>360</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.206522304676247</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.1402446877317285</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
         <v>211</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>16</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S9" s="3" t="n">
         <v>-0.3380397400935387</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T9" s="3" t="n">
         <v>-0.3380397400935387</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>150</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>-70</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.5106647038619894</v>
       </c>
     </row>
@@ -4923,7 +5419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5121,10 +5617,10 @@
         <v>0.1032426212645823</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.08367967670060686</v>
+        <v>0.06633642004451878</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -5202,10 +5698,10 @@
         <v>0.08442450091433044</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.06993138750699741</v>
+        <v>0.05543756953743766</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -5283,10 +5779,10 @@
         <v>0.08882055381815625</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.07701437681681529</v>
+        <v>0.06105255483079631</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -5326,12 +5822,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5346,28 +5842,28 @@
         <v>45755</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45904</v>
+        <v>45917</v>
       </c>
       <c r="G5" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="J5" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.06216000016109517</v>
+        <v>0.06321320299387231</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.06216000016109517</v>
+        <v>0.05173160794390522</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -5383,36 +5879,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="W5" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1783604398064753</v>
+        <v>0.1374994254296262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5427,28 +5923,28 @@
         <v>45755</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45840</v>
+        <v>45904</v>
       </c>
       <c r="G6" t="n">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="J6" t="n">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.09126633999965644</v>
+        <v>0.06216000016109517</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.07519549547653598</v>
+        <v>0.04927686199609638</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -5464,36 +5960,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.2332321541276028</v>
+        <v>0.1783604398064753</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5508,28 +6004,28 @@
         <v>45755</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45832</v>
+        <v>45840</v>
       </c>
       <c r="G7" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="J7" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09334112666390186</v>
+        <v>0.09126633999965644</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.07438277583171804</v>
+        <v>0.05961065063903417</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -5545,36 +6041,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="W7" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2446603617459924</v>
+        <v>0.2332321541276028</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5589,28 +6085,28 @@
         <v>45755</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45838</v>
+        <v>45832</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1711634614757399</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1711634614757399</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="J8" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.08170799359290759</v>
+        <v>0.09334112666390186</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.06659244470335765</v>
+        <v>0.05896637339200361</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -5626,24 +6122,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>52</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.2446603617459924</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="G9" t="n">
+        <v>90</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.1711634614757399</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.1711634614757399</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>89</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.08170799359290759</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.05279064831283325</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.1711634614757399</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.1711634614757399</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>56</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>1</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.2065105162719971</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_monthly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -882,12 +882,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -896,28 +896,28 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>39442</v>
+        <v>39364</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40533</v>
+        <v>40911</v>
       </c>
       <c r="G5" t="n">
-        <v>753</v>
+        <v>1067</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="J5" t="n">
-        <v>752</v>
+        <v>1066</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1599384989554068</v>
+        <v>0.1974000942251045</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -927,25 +927,25 @@
       </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>452</v>
+        <v>712</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>0.5986632950171407</v>
+        <v>0.837551214756322</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -992,25 +992,25 @@
         <v>39364</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>39881</v>
+        <v>39877</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40911</v>
+        <v>41394</v>
       </c>
       <c r="G6" t="n">
-        <v>1067</v>
+        <v>1398</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="J6" t="n">
-        <v>1066</v>
+        <v>1397</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1974000942251045</v>
+        <v>0.2811987286404182</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1020,60 +1020,60 @@
       </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>712</v>
+        <v>1045</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>0.837551214756322</v>
+        <v>1.602643947220918</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1088,22 +1088,22 @@
         <v>39877</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41394</v>
+        <v>41477</v>
       </c>
       <c r="G7" t="n">
-        <v>1398</v>
+        <v>1455</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="J7" t="n">
-        <v>1397</v>
+        <v>1454</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2811987286404182</v>
+        <v>0.2848395462178512</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1117,21 +1117,21 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1045</v>
+        <v>1102</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>1.602643947220918</v>
+        <v>1.564103658296977</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>0.6666666666666666</v>
@@ -1150,23 +1150,23 @@
         </is>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1187,16 +1187,16 @@
         <v>1455</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.6146619938319895</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.6146619938319895</v>
       </c>
       <c r="J8" t="n">
         <v>1454</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2848395462178512</v>
+        <v>0.298279648000863</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -1210,10 +1210,10 @@
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.6146619938319895</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.6146619938319895</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1224,7 +1224,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>1.564103658296977</v>
+        <v>1.595124238962278</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0.6666666666666666</v>
@@ -1243,102 +1243,9 @@
         </is>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AC8" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>39877</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>41477</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1455</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.6146619938319895</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.6146619938319895</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1454</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.298279648000863</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>353</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" s="3" t="n">
-        <v>-0.6146619938319895</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>-0.6146619938319895</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1102</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" s="3" t="n">
-        <v>1.595124238962278</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1355,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1752,12 +1659,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1772,25 +1679,25 @@
         <v>37460</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>37783</v>
+        <v>38012</v>
       </c>
       <c r="G5" t="n">
-        <v>806</v>
+        <v>963</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2185683866529438</v>
+        <v>-0.3030216391542161</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.3432461105733071</v>
       </c>
       <c r="J5" t="n">
-        <v>292</v>
+        <v>829</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1252308092487745</v>
+        <v>0.1481278166620073</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.08167972914679614</v>
+        <v>0.1055945425444167</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>39364</v>
@@ -1809,34 +1716,34 @@
         <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2185683866529438</v>
+        <v>-0.3030216391542161</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.3432461105733071</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>223</v>
+        <v>380</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.2797025138473266</v>
+        <v>0.4347647734522189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1848,28 +1755,28 @@
         <v>36608</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37460</v>
+        <v>37538</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38012</v>
+        <v>38957</v>
       </c>
       <c r="G6" t="n">
-        <v>963</v>
+        <v>1616</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.3687277122325638</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.3857020660410981</v>
       </c>
       <c r="J6" t="n">
-        <v>829</v>
+        <v>1586</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1481278166620073</v>
+        <v>0.1480346777153202</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1055945425444167</v>
+        <v>0.1366736544747824</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>39364</v>
@@ -1882,40 +1789,40 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>583</v>
+        <v>638</v>
       </c>
       <c r="R6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.3687277122325638</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.3857020660410981</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>380</v>
+        <v>978</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
         <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4347647734522189</v>
+        <v>0.5841024853737995</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1930,25 +1837,25 @@
         <v>37538</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38957</v>
+        <v>38944</v>
       </c>
       <c r="G7" t="n">
-        <v>1616</v>
+        <v>1607</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3687277122325638</v>
+        <v>-0.3754608976947175</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.3957852429007654</v>
       </c>
       <c r="J7" t="n">
-        <v>1586</v>
+        <v>1572</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1480346777153202</v>
+        <v>0.1513752318139535</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1366736544747824</v>
+        <v>0.1393683562842672</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>39364</v>
@@ -1967,34 +1874,34 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3687277122325638</v>
+        <v>-0.3754608976947175</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.3957852429007654</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5841024853737995</v>
+        <v>0.601180768840295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2009,25 +1916,25 @@
         <v>37538</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38944</v>
+        <v>38728</v>
       </c>
       <c r="G8" t="n">
-        <v>1607</v>
+        <v>1458</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3754608976947175</v>
+        <v>-0.3976227638230778</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="J8" t="n">
-        <v>1572</v>
+        <v>1386</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1513752318139535</v>
+        <v>0.1716566383260633</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1393683562842672</v>
+        <v>0.1505409261939787</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>39364</v>
@@ -2046,101 +1953,22 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3754608976947175</v>
+        <v>-0.3976227638230778</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>969</v>
+        <v>820</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.601180768840295</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>38728</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1458</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.3976227638230778</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.4221174890977989</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1386</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.1716566383260633</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.1505409261939787</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>638</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.3976227638230778</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.4221174890977989</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>820</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.6600892927937492</v>
       </c>
     </row>
@@ -2155,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2558,12 +2386,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2578,25 +2406,25 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40533</v>
+        <v>40911</v>
       </c>
       <c r="G5" t="n">
-        <v>807</v>
+        <v>1067</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="J5" t="n">
-        <v>805</v>
+        <v>1066</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1546755474705558</v>
+        <v>0.1974000942251041</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.08370501759350023</v>
+        <v>0.1228166173480004</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>43364</v>
@@ -2615,36 +2443,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>452</v>
+        <v>712</v>
       </c>
       <c r="W5" t="n">
-        <v>-408</v>
+        <v>-148</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.5983357204467421</v>
+        <v>0.8375512147563215</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2656,28 +2484,28 @@
         <v>39364</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>39881</v>
+        <v>39877</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40911</v>
+        <v>41394</v>
       </c>
       <c r="G6" t="n">
-        <v>1067</v>
+        <v>1398</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="J6" t="n">
-        <v>1066</v>
+        <v>1397</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1974000942251041</v>
+        <v>0.2811987286404189</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1228166173480004</v>
+        <v>0.2002379359033743</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>43364</v>
@@ -2690,42 +2518,42 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>712</v>
+        <v>1045</v>
       </c>
       <c r="W6" t="n">
-        <v>-148</v>
+        <v>185</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.8375512147563215</v>
+        <v>1.602643947220921</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2740,25 +2568,25 @@
         <v>39877</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41394</v>
+        <v>41477</v>
       </c>
       <c r="G7" t="n">
-        <v>1398</v>
+        <v>1455</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="J7" t="n">
-        <v>1397</v>
+        <v>1454</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2811987286404189</v>
+        <v>0.2848395462178516</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2002379359033743</v>
+        <v>0.2069212638990652</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>43364</v>
@@ -2777,36 +2605,36 @@
         <v>-2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1045</v>
+        <v>1102</v>
       </c>
       <c r="W7" t="n">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.602643947220921</v>
+        <v>1.564103658296978</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2827,19 +2655,19 @@
         <v>1455</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="J8" t="n">
         <v>1454</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2848395462178516</v>
+        <v>0.2982796480008626</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.2069212638990652</v>
+        <v>0.2166848058116959</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>43364</v>
@@ -2858,10 +2686,10 @@
         <v>-2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -2876,87 +2704,6 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.564103658296978</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>39877</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>41477</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1455</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.6146619938319893</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.6146619938319893</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1454</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.2982796480008626</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.2166848058116959</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>353</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.6146619938319893</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.6146619938319893</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1102</v>
-      </c>
-      <c r="W9" t="n">
-        <v>242</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>1.595124238962276</v>
       </c>
     </row>
@@ -2971,7 +2718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3374,12 +3121,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3394,25 +3141,25 @@
         <v>43458</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43563</v>
+        <v>43545</v>
       </c>
       <c r="G5" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="J5" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04849898132196487</v>
+        <v>0.04899572133157781</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.03006079347508416</v>
+        <v>0.02899795472484739</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>43880</v>
@@ -3431,36 +3178,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="W5" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1574905164302043</v>
+        <v>0.1662852001652733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3475,25 +3222,25 @@
         <v>43458</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43545</v>
+        <v>43557</v>
       </c>
       <c r="G6" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="J6" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.06265132539194433</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.02899795472484739</v>
+        <v>0.03825741284413761</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>43880</v>
@@ -3512,36 +3259,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="W6" t="n">
-        <v>-17</v>
+        <v>-9</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.2201474290648269</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3556,25 +3303,25 @@
         <v>43458</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43557</v>
+        <v>43537</v>
       </c>
       <c r="G7" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1756429698727684</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1758389292270287</v>
       </c>
       <c r="J7" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06265132539194433</v>
+        <v>0.06178239628542021</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.03825741284413761</v>
+        <v>0.03567008312656749</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>43880</v>
@@ -3593,36 +3340,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1756429698727684</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1758389292270287</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="W7" t="n">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2201474290648269</v>
+        <v>0.2130666245979118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3637,25 +3384,25 @@
         <v>43458</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43537</v>
+        <v>43528</v>
       </c>
       <c r="G8" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.161539993759288</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.161539993759288</v>
       </c>
       <c r="J8" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.06178239628542021</v>
+        <v>0.05450903553707552</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.03567008312656749</v>
+        <v>0.03052308008950504</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>43880</v>
@@ -3674,105 +3421,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.161539993759288</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.161539993759288</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="W8" t="n">
-        <v>-23</v>
+        <v>-30</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.2130666245979118</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>43528</v>
-      </c>
-      <c r="G9" t="n">
-        <v>110</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.161539993759288</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.161539993759288</v>
-      </c>
-      <c r="J9" t="n">
-        <v>109</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.05450903553707552</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.03052308008950504</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.161539993759288</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.161539993759288</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>46</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-30</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.1926627299536476</v>
       </c>
     </row>
@@ -3787,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4190,12 +3856,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4210,25 +3876,25 @@
         <v>43913</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>44055</v>
+        <v>44061</v>
       </c>
       <c r="G5" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="J5" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1193940004707371</v>
+        <v>0.1183626651723915</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.0608199262236669</v>
+        <v>0.0612671142774218</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>44564</v>
@@ -4247,36 +3913,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="W5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4071307910896131</v>
+        <v>0.4203549201436105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4291,25 +3957,25 @@
         <v>43913</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>44061</v>
+        <v>44055</v>
       </c>
       <c r="G6" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="J6" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1183626651723915</v>
+        <v>0.1330355594692814</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.0612671142774218</v>
+        <v>0.06776900748902423</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>44564</v>
@@ -4328,36 +3994,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="W6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.4760691587711159</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4372,25 +4038,25 @@
         <v>43913</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>44055</v>
+        <v>44076</v>
       </c>
       <c r="G7" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="J7" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1330355594692814</v>
+        <v>0.1443875768739651</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.06776900748902423</v>
+        <v>0.07790766720830088</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>44564</v>
@@ -4409,36 +4075,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="W7" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4760691587711159</v>
+        <v>0.5179689914546388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4453,25 +4119,25 @@
         <v>43913</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>44076</v>
+        <v>44069</v>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="J8" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1443875768739651</v>
+        <v>0.1293734448870105</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.07790766720830088</v>
+        <v>0.06853016731044111</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>44564</v>
@@ -4490,105 +4156,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="W8" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.5179689914546388</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="G9" t="n">
-        <v>132</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="J9" t="n">
-        <v>131</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.1293734448870105</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.06853016731044111</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>23</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>109</v>
-      </c>
-      <c r="W9" t="n">
-        <v>54</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.4722294238110734</v>
       </c>
     </row>
@@ -4603,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5006,12 +4591,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5023,28 +4608,28 @@
         <v>44564</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44729</v>
+        <v>44846</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45317</v>
+        <v>45135</v>
       </c>
       <c r="G5" t="n">
-        <v>518</v>
+        <v>393</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="J5" t="n">
-        <v>517</v>
+        <v>392</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1212946577391739</v>
+        <v>0.1318162553441144</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.0986257965760659</v>
+        <v>0.09338610296468229</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>45707</v>
@@ -5057,42 +4642,42 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="R5" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>403</v>
+        <v>198</v>
       </c>
       <c r="W5" t="n">
-        <v>183</v>
+        <v>-22</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.2858663094007141</v>
+        <v>0.3119225417387239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5104,28 +4689,28 @@
         <v>44564</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44846</v>
+        <v>44848</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45135</v>
+        <v>45092</v>
       </c>
       <c r="G6" t="n">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="J6" t="n">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1318162553441144</v>
+        <v>0.2035103799588042</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.09338610296468229</v>
+        <v>0.138770824610914</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>45707</v>
@@ -5138,42 +4723,42 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="W6" t="n">
-        <v>-22</v>
+        <v>-53</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.3119225417387239</v>
+        <v>0.4897834485477317</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5194,19 +4779,19 @@
         <v>364</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="J7" t="n">
         <v>363</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2035103799588042</v>
+        <v>0.2115738387606444</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.138770824610914</v>
+        <v>0.1442691821265061</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>45707</v>
@@ -5225,10 +4810,10 @@
         <v>2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -5243,18 +4828,18 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4897834485477317</v>
+        <v>0.5108619332907343</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5266,28 +4851,28 @@
         <v>44564</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44848</v>
+        <v>44868</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45092</v>
+        <v>45089</v>
       </c>
       <c r="G8" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3380397400935387</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3380397400935387</v>
       </c>
       <c r="J8" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2115738387606444</v>
+        <v>0.206522304676247</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1442691821265061</v>
+        <v>0.1402446877317285</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>45707</v>
@@ -5300,111 +4885,30 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3380397400935387</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3380397400935387</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="W8" t="n">
-        <v>-53</v>
+        <v>-70</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.5108619332907343</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>44868</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>45089</v>
-      </c>
-      <c r="G9" t="n">
-        <v>361</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.3380397400935387</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.3380397400935387</v>
-      </c>
-      <c r="J9" t="n">
-        <v>360</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.206522304676247</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.1402446877317285</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>211</v>
-      </c>
-      <c r="R9" t="n">
-        <v>16</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.3380397400935387</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.3380397400935387</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>150</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-70</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.5106647038619894</v>
       </c>
     </row>
@@ -5419,7 +4923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5822,12 +5326,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5842,25 +5346,25 @@
         <v>45755</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45917</v>
+        <v>45904</v>
       </c>
       <c r="G5" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="J5" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.06321320299387231</v>
+        <v>0.06216000016109517</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.05173160794390522</v>
+        <v>0.04927686199609638</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>46021</v>
@@ -5879,36 +5383,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="W5" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1374994254296262</v>
+        <v>0.1783604398064753</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5923,25 +5427,25 @@
         <v>45755</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45904</v>
+        <v>45840</v>
       </c>
       <c r="G6" t="n">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="J6" t="n">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.06216000016109517</v>
+        <v>0.09126633999965644</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.04927686199609638</v>
+        <v>0.05961065063903417</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>46021</v>
@@ -5960,36 +5464,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="W6" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.1783604398064753</v>
+        <v>0.2332321541276028</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6004,25 +5508,25 @@
         <v>45755</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45840</v>
+        <v>45832</v>
       </c>
       <c r="G7" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="J7" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09126633999965644</v>
+        <v>0.09334112666390186</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.05961065063903417</v>
+        <v>0.05896637339200361</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>46021</v>
@@ -6041,36 +5545,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2332321541276028</v>
+        <v>0.2446603617459924</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6085,25 +5589,25 @@
         <v>45755</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45832</v>
+        <v>45838</v>
       </c>
       <c r="G8" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1711634614757399</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1711634614757399</v>
       </c>
       <c r="J8" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.09334112666390186</v>
+        <v>0.08170799359290759</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.05896637339200361</v>
+        <v>0.05279064831283325</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>46021</v>
@@ -6122,105 +5626,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1711634614757399</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1711634614757399</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="W8" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.2446603617459924</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>45838</v>
-      </c>
-      <c r="G9" t="n">
-        <v>90</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.1711634614757399</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.1711634614757399</v>
-      </c>
-      <c r="J9" t="n">
-        <v>89</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.08170799359290759</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.05279064831283325</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>34</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.1711634614757399</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.1711634614757399</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>56</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.2065105162719971</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_monthly.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -762,27 +763,27 @@
         <v>1.253501048252387</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -855,27 +856,27 @@
         <v>1.176694263222226</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
     </row>
@@ -948,27 +949,27 @@
         <v>0.837551214756322</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1041,27 +1042,27 @@
         <v>1.602643947220918</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1134,27 +1135,27 @@
         <v>1.564103658296977</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1227,27 +1228,27 @@
         <v>1.595124238962278</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1436,66 +1437,68 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="G2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="J2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.0903200482301444</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.04076898034342899</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>-0.03939252582909292</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.9452989626493482</v>
+        <v>0.2044255219913533</v>
       </c>
     </row>
     <row r="3">
@@ -1515,34 +1518,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38980</v>
+        <v>36105</v>
       </c>
       <c r="G3" t="n">
-        <v>1632</v>
+        <v>79</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-0.3722353067637153</v>
+        <v>-0.168347525660839</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0.3927946397031032</v>
+        <v>-0.1698467665967934</v>
       </c>
       <c r="J3" t="n">
-        <v>1602</v>
+        <v>77</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.1651097235934952</v>
+        <v>0.09331271424016059</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1531905859315117</v>
+        <v>0.04038981632232292</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1552,29 +1555,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.3722353067637153</v>
+        <v>-0.168347525660839</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.3927946397031032</v>
+        <v>-0.1698467665967934</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1049</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-7</v>
+      </c>
       <c r="X3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.5929535553277914</v>
+        <v>0.2024253289147122</v>
       </c>
     </row>
     <row r="4">
@@ -1594,66 +1599,68 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>36118</v>
+      </c>
       <c r="G4" t="n">
-        <v>1896</v>
+        <v>88</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.5351953756562349</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0.5405877541480402</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="J4" t="n">
-        <v>1893</v>
+        <v>86</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.3318786120147709</v>
+        <v>0.08971493195499394</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.3318786120147709</v>
+        <v>0.04095866547233682</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>-0.07379561685859526</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.5351953756562349</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.5405877541480402</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1313</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
       <c r="X4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1.151441589919315</v>
+        <v>0.2058228721729791</v>
       </c>
     </row>
     <row r="5">
@@ -1673,34 +1680,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="G5" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="J5" t="n">
-        <v>829</v>
+        <v>77</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1481278166620073</v>
+        <v>0.08381851803583454</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1055945425444167</v>
+        <v>0.03605284870827317</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1710,29 +1717,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R5" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>380</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-8</v>
+      </c>
       <c r="X5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4347647734522189</v>
+        <v>0.1846197916504295</v>
       </c>
     </row>
     <row r="6">
@@ -1752,34 +1761,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38957</v>
+        <v>36119</v>
       </c>
       <c r="G6" t="n">
-        <v>1616</v>
+        <v>89</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3687277122325638</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="J6" t="n">
-        <v>1586</v>
+        <v>87</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1480346777153202</v>
+        <v>0.1103597356015969</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1366736544747824</v>
+        <v>0.05066615746607198</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -1789,29 +1798,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3687277122325638</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>978</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
       <c r="X6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.5841024853737995</v>
+        <v>0.2414902277807456</v>
       </c>
     </row>
     <row r="7">
@@ -1831,34 +1842,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38944</v>
+        <v>36119</v>
       </c>
       <c r="G7" t="n">
-        <v>1607</v>
+        <v>89</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3754608976947175</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="J7" t="n">
-        <v>1572</v>
+        <v>87</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1513752318139535</v>
+        <v>0.1106615069328753</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1393683562842672</v>
+        <v>0.05080470069205879</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1868,29 +1879,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3754608976947175</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>969</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
       <c r="X7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.601180768840295</v>
+        <v>0.2436869610882062</v>
       </c>
     </row>
     <row r="8">
@@ -1910,34 +1923,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38728</v>
+        <v>36105</v>
       </c>
       <c r="G8" t="n">
-        <v>1458</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3976227638230778</v>
+        <v>-0.1729041606870662</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4221174890977989</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="J8" t="n">
-        <v>1386</v>
+        <v>77</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1716566383260633</v>
+        <v>0.1007954710930635</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1505409261939787</v>
+        <v>0.0436286801506272</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1947,29 +1960,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3976227638230778</v>
+        <v>-0.1729041606870662</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.4221174890977989</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>820</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-7</v>
+      </c>
       <c r="X8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.6600892927937492</v>
+        <v>0.2090497285425799</v>
       </c>
     </row>
   </sheetData>
@@ -2157,68 +2172,66 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.503509252857314</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.2352416489517779</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.1561727120528913</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>-0.03993583465459927</v>
+      </c>
       <c r="Q2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>860</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>1.014136226616547</v>
+        <v>0.9463998245842122</v>
       </c>
     </row>
     <row r="3">
@@ -2238,34 +2251,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>38975</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1628</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.37101411487914</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.3927946397031032</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1596</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1653065285673719</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1532256179322682</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>41324</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1349</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.556246046224159</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.556246046224159</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1348</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.2498952241815955</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.1748030436662044</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -2275,31 +2288,29 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.556246046224159</v>
+        <v>-0.37101411487914</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.556246046224159</v>
+        <v>-0.3927946397031032</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>994</v>
-      </c>
-      <c r="W3" t="n">
-        <v>134</v>
-      </c>
+        <v>1046</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>1.253501048252389</v>
+        <v>0.589860796014285</v>
       </c>
     </row>
     <row r="4">
@@ -2319,68 +2330,66 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.5364587231151221</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.5405877541480402</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1894</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.331966121208649</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.331966121208649</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>40568</v>
-      </c>
-      <c r="G4" t="n">
-        <v>830</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.4375057689528339</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.4456113326384448</v>
-      </c>
-      <c r="J4" t="n">
-        <v>816</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.2093201856322416</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.1148777108501162</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>-0.07631305728962323</v>
+      </c>
       <c r="Q4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.4375057689528339</v>
+        <v>-0.5364587231151221</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.4456113326384448</v>
+        <v>-0.5405877541480402</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>475</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-385</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.7777960107045938</v>
+        <v>1.157305184816051</v>
       </c>
     </row>
     <row r="5">
@@ -2400,34 +2409,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>38012</v>
+      </c>
+      <c r="G5" t="n">
+        <v>962</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.3013243461981798</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.343246110573307</v>
+      </c>
+      <c r="J5" t="n">
+        <v>813</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1482043849238123</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.1056221565201652</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>40911</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1067</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1066</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.1974000942251041</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.1228166173480004</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -2437,31 +2446,29 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3013243461981798</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>712</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-148</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.8375512147563215</v>
+        <v>0.4312792989973724</v>
       </c>
     </row>
     <row r="6">
@@ -2481,34 +2488,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>38957</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1615</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.3701203966363426</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.385702066041098</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1590</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.14808047344038</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.136709692353978</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>39877</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>41394</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1398</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.6157753345140465</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.6157753345140465</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1397</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.2811987286404189</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.2002379359033743</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -2518,31 +2525,29 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>353</v>
+        <v>637</v>
       </c>
       <c r="R6" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.3701203966363426</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.385702066041098</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1045</v>
-      </c>
-      <c r="W6" t="n">
-        <v>185</v>
-      </c>
+        <v>978</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1.602643947220921</v>
+        <v>0.5876049877783638</v>
       </c>
     </row>
     <row r="7">
@@ -2562,34 +2567,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>38944</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1606</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.375472295585537</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.3957852429007653</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1572</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.1514223231922318</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.1394051046979009</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>39877</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>41477</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1455</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.6100001664268992</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.6100001664268992</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1454</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.2848395462178516</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.2069212638990652</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -2599,31 +2604,29 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>353</v>
+        <v>637</v>
       </c>
       <c r="R7" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.375472295585537</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.3957852429007653</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1102</v>
-      </c>
-      <c r="W7" t="n">
-        <v>242</v>
-      </c>
+        <v>969</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.564103658296978</v>
+        <v>0.6012099910564699</v>
       </c>
     </row>
     <row r="8">
@@ -2643,34 +2646,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>38723</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1454</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.3950032996914197</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.4221174890977989</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1365</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.1718818990353882</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.1505713948143466</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>39877</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>41477</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1455</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.6146619938319893</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.6146619938319893</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1454</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.2982796480008626</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.2166848058116959</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -2680,31 +2683,29 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>353</v>
+        <v>637</v>
       </c>
       <c r="R8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.3950032996914197</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1102</v>
-      </c>
-      <c r="W8" t="n">
-        <v>242</v>
-      </c>
+        <v>817</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.595124238962276</v>
+        <v>0.652901576967192</v>
       </c>
     </row>
   </sheetData>
@@ -2892,34 +2893,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="G2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="J2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.08269444253856417</v>
+        <v>0.2352416489517779</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.0521896337568788</v>
+        <v>0.1562010221613542</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2929,22 +2930,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -2953,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.2429105460160741</v>
+        <v>1.014136226616547</v>
       </c>
     </row>
     <row r="3">
@@ -2973,34 +2974,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>43545</v>
+        <v>41324</v>
       </c>
       <c r="G3" t="n">
-        <v>123</v>
+        <v>1349</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-0.1661942153206122</v>
+        <v>-0.556246046224159</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0.1661942153206122</v>
+        <v>-0.556246046224159</v>
       </c>
       <c r="J3" t="n">
-        <v>122</v>
+        <v>1348</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05923389423926628</v>
+        <v>0.2498952241815955</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.0350573833111343</v>
+        <v>0.1748347309761114</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3010,31 +3011,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.1661942153206122</v>
+        <v>-0.556246046224159</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.1661942153206122</v>
+        <v>-0.556246046224159</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>59</v>
+        <v>994</v>
       </c>
       <c r="W3" t="n">
-        <v>-17</v>
+        <v>134</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.1993200555504859</v>
+        <v>1.253501048252389</v>
       </c>
     </row>
     <row r="4">
@@ -3054,34 +3055,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43588</v>
+        <v>40568</v>
       </c>
       <c r="G4" t="n">
-        <v>153</v>
+        <v>830</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.4375057689528339</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.4456113326384448</v>
       </c>
       <c r="J4" t="n">
-        <v>148</v>
+        <v>816</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.07930286943495034</v>
+        <v>0.2093201856322416</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.05230553290603873</v>
+        <v>0.1148985352336554</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3091,31 +3092,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.4375057689528339</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.4456113326384448</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>89</v>
+        <v>475</v>
       </c>
       <c r="W4" t="n">
-        <v>13</v>
+        <v>-385</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.2457029538737467</v>
+        <v>0.7777960107045938</v>
       </c>
     </row>
     <row r="5">
@@ -3135,34 +3136,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43545</v>
+        <v>40911</v>
       </c>
       <c r="G5" t="n">
-        <v>123</v>
+        <v>1067</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="J5" t="n">
-        <v>119</v>
+        <v>1066</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.1974000942251041</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.02899795472484739</v>
+        <v>0.1228388808517359</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3172,31 +3173,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>59</v>
+        <v>712</v>
       </c>
       <c r="W5" t="n">
-        <v>-17</v>
+        <v>-148</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.8375512147563215</v>
       </c>
     </row>
     <row r="6">
@@ -3216,34 +3217,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43458</v>
+        <v>39877</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43557</v>
+        <v>41394</v>
       </c>
       <c r="G6" t="n">
-        <v>131</v>
+        <v>1398</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="J6" t="n">
-        <v>130</v>
+        <v>1397</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.06265132539194433</v>
+        <v>0.2811987286404189</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.03825741284413761</v>
+        <v>0.2002742339070991</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3253,31 +3254,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>353</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>67</v>
+        <v>1045</v>
       </c>
       <c r="W6" t="n">
-        <v>-9</v>
+        <v>185</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.2201474290648269</v>
+        <v>1.602643947220921</v>
       </c>
     </row>
     <row r="7">
@@ -3297,34 +3298,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>43458</v>
+        <v>39877</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43537</v>
+        <v>41477</v>
       </c>
       <c r="G7" t="n">
-        <v>117</v>
+        <v>1455</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="J7" t="n">
-        <v>115</v>
+        <v>1454</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06178239628542021</v>
+        <v>0.2848395462178516</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.03567008312656749</v>
+        <v>0.2069587734187967</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -3334,31 +3335,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>64</v>
+        <v>353</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>53</v>
+        <v>1102</v>
       </c>
       <c r="W7" t="n">
-        <v>-23</v>
+        <v>242</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2130666245979118</v>
+        <v>1.564103658296978</v>
       </c>
     </row>
     <row r="8">
@@ -3378,34 +3379,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>43458</v>
+        <v>39877</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43528</v>
+        <v>41477</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>1455</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="J8" t="n">
-        <v>109</v>
+        <v>1454</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.05450903553707552</v>
+        <v>0.2982796480008626</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.03052308008950504</v>
+        <v>0.2167240852112412</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -3415,31 +3416,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>353</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>46</v>
+        <v>1102</v>
       </c>
       <c r="W8" t="n">
-        <v>-30</v>
+        <v>242</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.1926627299536476</v>
+        <v>1.595124238962276</v>
       </c>
     </row>
   </sheetData>
@@ -3627,34 +3628,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="G2" t="n">
+        <v>143</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.1989728318606706</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.2022979914860074</v>
+      </c>
+      <c r="J2" t="n">
+        <v>138</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.08183226369428352</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.05211846719049091</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="G2" t="n">
-        <v>78</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="J2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -3664,22 +3665,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -3688,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.4088864968986547</v>
+        <v>0.2483971078320051</v>
       </c>
     </row>
     <row r="3">
@@ -3708,34 +3709,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>43557</v>
+      </c>
+      <c r="G3" t="n">
+        <v>132</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.1673913441411503</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.1673913441411503</v>
+      </c>
+      <c r="J3" t="n">
+        <v>131</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.05835513570210118</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.03571829561387335</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>44053</v>
-      </c>
-      <c r="G3" t="n">
-        <v>120</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.3081513905894094</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.3081513905894094</v>
-      </c>
-      <c r="J3" t="n">
-        <v>119</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.1285134533062128</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.06493100247990062</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3745,31 +3746,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.3081513905894094</v>
+        <v>-0.1673913441411503</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.3081513905894094</v>
+        <v>-0.1673913441411503</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="W3" t="n">
-        <v>42</v>
+        <v>-11</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.4454029196530931</v>
+        <v>0.2010444438251526</v>
       </c>
     </row>
     <row r="4">
@@ -3789,34 +3790,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>43636</v>
+      </c>
+      <c r="G4" t="n">
+        <v>187</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.1991277646524821</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.1991277646524821</v>
+      </c>
+      <c r="J4" t="n">
+        <v>186</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.07312544540501786</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.05321490270851575</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>44046</v>
-      </c>
-      <c r="G4" t="n">
-        <v>115</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.3158142431874948</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.3158142431874948</v>
-      </c>
-      <c r="J4" t="n">
-        <v>114</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.1291668938515992</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.06389855538410746</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3826,31 +3827,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="W4" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.4615913734580137</v>
+        <v>0.2486386165779311</v>
       </c>
     </row>
     <row r="5">
@@ -3870,34 +3871,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>43545</v>
+      </c>
+      <c r="G5" t="n">
+        <v>124</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.1419538085967058</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.1452798889626854</v>
+      </c>
+      <c r="J5" t="n">
+        <v>118</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.04879934490473427</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.02895708373240715</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>44061</v>
-      </c>
-      <c r="G5" t="n">
-        <v>126</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="J5" t="n">
-        <v>125</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.1183626651723915</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.0612671142774218</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3907,31 +3908,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="W5" t="n">
-        <v>48</v>
+        <v>-19</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.1654384228016292</v>
       </c>
     </row>
     <row r="6">
@@ -3951,34 +3952,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="G6" t="n">
+        <v>134</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.1829533120643722</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.1829533120643722</v>
+      </c>
+      <c r="J6" t="n">
+        <v>133</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.06424234517826913</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.03961631664809385</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="G6" t="n">
-        <v>122</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.3225249683879728</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.3225249683879728</v>
-      </c>
-      <c r="J6" t="n">
-        <v>121</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.1330355594692814</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.06776900748902423</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3988,31 +3989,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="W6" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4760691587711159</v>
+        <v>0.2239202664496773</v>
       </c>
     </row>
     <row r="7">
@@ -4032,34 +4033,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="G7" t="n">
+        <v>118</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.1783446632793302</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.1783446632793302</v>
+      </c>
+      <c r="J7" t="n">
+        <v>117</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.06381830295717236</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.03694915879991898</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>44076</v>
-      </c>
-      <c r="G7" t="n">
-        <v>137</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.341225014720676</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.341225014720676</v>
-      </c>
-      <c r="J7" t="n">
-        <v>136</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.1443875768739651</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.07790766720830088</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4069,31 +4070,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="W7" t="n">
-        <v>59</v>
+        <v>-25</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5179689914546388</v>
+        <v>0.2170553215063706</v>
       </c>
     </row>
     <row r="8">
@@ -4113,34 +4114,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>43529</v>
+      </c>
+      <c r="G8" t="n">
+        <v>112</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.1630780308514724</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.1630780308514724</v>
+      </c>
+      <c r="J8" t="n">
+        <v>111</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.05536896920771481</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.03123859435247722</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="G8" t="n">
-        <v>132</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="J8" t="n">
-        <v>131</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.1293734448870105</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.06853016731044111</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4150,31 +4151,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="W8" t="n">
-        <v>54</v>
+        <v>-31</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.4722294238110734</v>
+        <v>0.1948545227189886</v>
       </c>
     </row>
   </sheetData>
@@ -4362,34 +4363,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="J2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="G2" t="n">
-        <v>473</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="J2" t="n">
-        <v>472</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -4399,22 +4400,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -4423,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.4792042812088524</v>
+        <v>0.4088864968986547</v>
       </c>
     </row>
     <row r="3">
@@ -4443,34 +4444,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>44053</v>
+      </c>
+      <c r="G3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.3081513905894094</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.3081513905894094</v>
+      </c>
+      <c r="J3" t="n">
+        <v>119</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1285134533062128</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.06493100247990062</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>45125</v>
-      </c>
-      <c r="G3" t="n">
-        <v>385</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.291261694520513</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.291261694520513</v>
-      </c>
-      <c r="J3" t="n">
-        <v>384</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.1702877757340237</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.1194104395028351</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -4480,31 +4481,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.291261694520513</v>
+        <v>-0.3081513905894094</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.291261694520513</v>
+        <v>-0.3081513905894094</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>190</v>
+        <v>97</v>
       </c>
       <c r="W3" t="n">
-        <v>-30</v>
+        <v>42</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.410958025365179</v>
+        <v>0.4454029196530931</v>
       </c>
     </row>
     <row r="4">
@@ -4524,34 +4525,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>44046</v>
+      </c>
+      <c r="G4" t="n">
+        <v>115</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.3158142431874948</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.3158142431874948</v>
+      </c>
+      <c r="J4" t="n">
+        <v>114</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.1291668938515992</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.06389855538410746</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>45125</v>
-      </c>
-      <c r="G4" t="n">
-        <v>385</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.2867967086275238</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.2867967086275238</v>
-      </c>
-      <c r="J4" t="n">
-        <v>384</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.1845225032964088</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.1293922192700595</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -4561,31 +4562,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="R4" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.2867967086275238</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.2867967086275238</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="W4" t="n">
-        <v>-88</v>
+        <v>37</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.4021247687677061</v>
+        <v>0.4615913734580137</v>
       </c>
     </row>
     <row r="5">
@@ -4605,34 +4606,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>44061</v>
+      </c>
+      <c r="G5" t="n">
+        <v>126</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="J5" t="n">
+        <v>125</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1183626651723915</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.0612671142774218</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>45135</v>
-      </c>
-      <c r="G5" t="n">
-        <v>393</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.2377598766809245</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.2377598766809245</v>
-      </c>
-      <c r="J5" t="n">
-        <v>392</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.1318162553441144</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.09338610296468229</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -4642,31 +4643,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="W5" t="n">
-        <v>-22</v>
+        <v>48</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.3119225417387239</v>
+        <v>0.4203549201436105</v>
       </c>
     </row>
     <row r="6">
@@ -4686,34 +4687,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="G6" t="n">
+        <v>122</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.3225249683879728</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.3225249683879728</v>
+      </c>
+      <c r="J6" t="n">
+        <v>121</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.1330355594692814</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.06776900748902423</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="G6" t="n">
-        <v>364</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.3287615049188402</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.3287615049188402</v>
-      </c>
-      <c r="J6" t="n">
-        <v>363</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.2035103799588042</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.138770824610914</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -4723,31 +4724,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="W6" t="n">
-        <v>-53</v>
+        <v>44</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4897834485477317</v>
+        <v>0.4760691587711159</v>
       </c>
     </row>
     <row r="7">
@@ -4767,34 +4768,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="G7" t="n">
+        <v>137</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="J7" t="n">
+        <v>136</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.1443875768739651</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.07790766720830088</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="G7" t="n">
-        <v>364</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.3381261530483139</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.3381261530483139</v>
-      </c>
-      <c r="J7" t="n">
-        <v>363</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.2115738387606444</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.1442691821265061</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4804,31 +4805,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="W7" t="n">
-        <v>-53</v>
+        <v>59</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5108619332907343</v>
+        <v>0.5179689914546388</v>
       </c>
     </row>
     <row r="8">
@@ -4848,34 +4849,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="G8" t="n">
+        <v>132</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.3207580395918463</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.3207580395918463</v>
+      </c>
+      <c r="J8" t="n">
+        <v>131</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.1293734448870105</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.06853016731044111</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>44868</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>45089</v>
-      </c>
-      <c r="G8" t="n">
-        <v>361</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.3380397400935387</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.3380397400935387</v>
-      </c>
-      <c r="J8" t="n">
-        <v>360</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.206522304676247</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.1402446877317285</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4885,31 +4886,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>211</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3380397400935387</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3380397400935387</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="W8" t="n">
-        <v>-70</v>
+        <v>54</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.5106647038619894</v>
+        <v>0.4722294238110734</v>
       </c>
     </row>
   </sheetData>
@@ -5097,6 +5098,741 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="G2" t="n">
+        <v>473</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="J2" t="n">
+        <v>472</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>253</v>
+      </c>
+      <c r="R2" t="n">
+        <v>58</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>220</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>0.4792042812088524</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>equal_weight</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>equal_t_10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>45125</v>
+      </c>
+      <c r="G3" t="n">
+        <v>385</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.291261694520513</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.291261694520513</v>
+      </c>
+      <c r="J3" t="n">
+        <v>384</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1702877757340237</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1194104395028351</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>-0.291261694520513</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-0.291261694520513</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>190</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>0.410958025365179</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>45125</v>
+      </c>
+      <c r="G4" t="n">
+        <v>385</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.2867967086275238</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.2867967086275238</v>
+      </c>
+      <c r="J4" t="n">
+        <v>384</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.1845225032964088</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1293922192700595</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>253</v>
+      </c>
+      <c r="R4" t="n">
+        <v>58</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.2867967086275238</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-0.2867967086275238</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>132</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-88</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0.4021247687677061</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>45135</v>
+      </c>
+      <c r="G5" t="n">
+        <v>393</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="J5" t="n">
+        <v>392</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1318162553441144</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.09338610296468229</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>195</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>198</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-22</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0.3119225417387239</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="G6" t="n">
+        <v>364</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.3287615049188402</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.3287615049188402</v>
+      </c>
+      <c r="J6" t="n">
+        <v>363</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.2035103799588042</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.138770824610914</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>197</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-0.3287615049188402</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-0.3287615049188402</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>167</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-53</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0.4897834485477317</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="G7" t="n">
+        <v>364</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="J7" t="n">
+        <v>363</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.2115738387606444</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.1442691821265061</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>197</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>167</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-53</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0.5108619332907343</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>44868</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>45089</v>
+      </c>
+      <c r="G8" t="n">
+        <v>361</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.3380397400935387</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.3380397400935387</v>
+      </c>
+      <c r="J8" t="n">
+        <v>360</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.206522304676247</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.1402446877317285</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>211</v>
+      </c>
+      <c r="R8" t="n">
+        <v>16</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.3380397400935387</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.3380397400935387</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>150</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-70</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.5106647038619894</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="E2" s="2" t="n">
